--- a/extras/Research.xlsx
+++ b/extras/Research.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\source\Personal\SpaceGame\code\spacegame\extras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E55E005C-0A35-4F1E-A632-710F72333650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE0AB2D-88E1-4630-92EB-CD148B1D2DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D6D1989B-7307-4536-B229-6C0E72345249}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D6D1989B-7307-4536-B229-6C0E72345249}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="51">
   <si>
     <t>Node</t>
   </si>
@@ -83,15 +83,9 @@
     <t>Reduces Helium-3 cost of sub-light travel</t>
   </si>
   <si>
-    <t>FTL Efficiency</t>
-  </si>
-  <si>
     <t>Reduces Helium-3 cost of FTL jumps</t>
   </si>
   <si>
-    <t>Combat</t>
-  </si>
-  <si>
     <t>Ablative Plating</t>
   </si>
   <si>
@@ -104,9 +98,6 @@
     <t>Adaptive Composite</t>
   </si>
   <si>
-    <t>Armor ignores a portion of Beam Weapon damage</t>
-  </si>
-  <si>
     <t>Starship Upgrades</t>
   </si>
   <si>
@@ -149,22 +140,58 @@
     <t>Regenerative Field Emitters</t>
   </si>
   <si>
-    <t>Shields are more resistant to damage</t>
-  </si>
-  <si>
-    <t>Armor is more resistant to damage</t>
-  </si>
-  <si>
     <t>Tessellated Barrier</t>
   </si>
   <si>
-    <t>Increases shield efficiency</t>
-  </si>
-  <si>
     <t>Shields recharge faster</t>
   </si>
   <si>
     <t>Shields have a chance to ignore all damage</t>
+  </si>
+  <si>
+    <t>Plasma Exhaust Optimization</t>
+  </si>
+  <si>
+    <t>Slipstream Calibration</t>
+  </si>
+  <si>
+    <t>Emergency Thrust Capacitors</t>
+  </si>
+  <si>
+    <t>Low-emission drive</t>
+  </si>
+  <si>
+    <t>Reduces chance of being detected by enemy ships (reduces chance of random encounters)</t>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>Shields</t>
+  </si>
+  <si>
+    <t>Maneuvering Thruster Array</t>
+  </si>
+  <si>
+    <t>Allows for performing more precise combat maneuvers (increases ship defense)</t>
+  </si>
+  <si>
+    <t>Allows pilot to engage emergency thrusters in combat (new combat ability)</t>
+  </si>
+  <si>
+    <t>Armor is more resistant to damage (damage reduction vs all weapons)</t>
+  </si>
+  <si>
+    <t>Armor is more resistant to damage (increased damage reduction)</t>
+  </si>
+  <si>
+    <t>Shields are more resistant to damage (damage reduction vs all weapons)</t>
+  </si>
+  <si>
+    <t>Increases shield efficiency (increased defense against all weapons)</t>
+  </si>
+  <si>
+    <t>Emergency Thrust Capacitors and Maneuvering Thruster Array</t>
   </si>
 </sst>
 </file>
@@ -537,13 +564,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E798BFCC-08A9-4756-941C-6EE519A76616}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.28515625" customWidth="1"/>
-    <col min="4" max="4" width="58" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="82.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="71.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -560,7 +587,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -619,7 +646,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>13</v>
@@ -633,10 +660,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
@@ -646,224 +673,282 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
         <v>16</v>
       </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" t="s">
         <v>16</v>
-      </c>
-      <c r="B11">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" t="s">
-        <v>35</v>
+      <c r="E18" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26">
+        <v>2</v>
+      </c>
+      <c r="C26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
         <v>22</v>
       </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28">
+        <v>4</v>
+      </c>
+      <c r="C28" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B20">
-        <v>2</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="D28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29">
+        <v>5</v>
+      </c>
+      <c r="C29" t="s">
         <v>24</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D29" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B21">
-        <v>3</v>
-      </c>
-      <c r="C21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B22">
-        <v>4</v>
-      </c>
-      <c r="C22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B23">
-        <v>5</v>
-      </c>
-      <c r="C23" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/extras/Research.xlsx
+++ b/extras/Research.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\source\Personal\SpaceGame\code\spacegame\extras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE0AB2D-88E1-4630-92EB-CD148B1D2DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1F3884-945A-4E35-8EAD-892E9B6D038B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D6D1989B-7307-4536-B229-6C0E72345249}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="66">
   <si>
     <t>Node</t>
   </si>
@@ -86,6 +86,9 @@
     <t>Reduces Helium-3 cost of FTL jumps</t>
   </si>
   <si>
+    <t>Combat</t>
+  </si>
+  <si>
     <t>Ablative Plating</t>
   </si>
   <si>
@@ -140,6 +143,9 @@
     <t>Regenerative Field Emitters</t>
   </si>
   <si>
+    <t>Overcharge Capacitors</t>
+  </si>
+  <si>
     <t>Tessellated Barrier</t>
   </si>
   <si>
@@ -192,6 +198,45 @@
   </si>
   <si>
     <t>Emergency Thrust Capacitors and Maneuvering Thruster Array</t>
+  </si>
+  <si>
+    <t>Predictive Targeting Algorithms</t>
+  </si>
+  <si>
+    <t>Increases chance to hit with all weapons</t>
+  </si>
+  <si>
+    <t>Coherence Amplifier</t>
+  </si>
+  <si>
+    <t>Shaped Charge Warheads</t>
+  </si>
+  <si>
+    <t>Torpedoes better penetrate damage reduction</t>
+  </si>
+  <si>
+    <t>Split-Fire Targeting</t>
+  </si>
+  <si>
+    <t>Warhead Miniaturization</t>
+  </si>
+  <si>
+    <t>Smaller torpedo warheads allow for storing a larger quantity</t>
+  </si>
+  <si>
+    <t>Particle cannons better penetrate damage reduction</t>
+  </si>
+  <si>
+    <t>Particle cannons fire at one additional target</t>
+  </si>
+  <si>
+    <t>Allows for temporarily increasing the power to particle cannons (new combat ability)</t>
+  </si>
+  <si>
+    <t>Shield Disruption Emitter</t>
+  </si>
+  <si>
+    <t>Particle cannons have a chance to reduce enemy shield defense rating</t>
   </si>
 </sst>
 </file>
@@ -564,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E798BFCC-08A9-4756-941C-6EE519A76616}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
@@ -587,7 +632,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -646,7 +691,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>13</v>
@@ -660,7 +705,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>14</v>
@@ -677,13 +722,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -694,13 +739,13 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -711,244 +756,360 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13">
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B14">
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" t="s">
         <v>30</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B18">
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B19">
         <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>20</v>
+        <v>34</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" t="s">
-        <v>20</v>
+        <v>58</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B29">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31">
         <v>5</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C31" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" t="s">
         <v>24</v>
-      </c>
-      <c r="D29" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
